--- a/03_bloques/B02/B02_trabajo.xlsx
+++ b/03_bloques/B02/B02_trabajo.xlsx
@@ -638,7 +638,7 @@
       <c r="G3" s="3" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       <c r="G7" s="5" t="inlineStr"/>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
@@ -885,7 +885,7 @@
       <c r="G8" s="3" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1136,7 +1136,7 @@
       <c r="G13" s="5" t="inlineStr"/>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
@@ -1183,7 +1183,7 @@
       <c r="G14" s="3" t="inlineStr"/>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1332,7 +1332,7 @@
       <c r="G17" s="3" t="inlineStr"/>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1430,7 +1430,7 @@
       <c r="G19" s="5" t="inlineStr"/>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
@@ -1579,7 +1579,7 @@
       <c r="G22" s="3" t="inlineStr"/>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       <c r="G25" s="5" t="inlineStr"/>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -1928,7 +1928,7 @@
       <c r="G29" s="3" t="inlineStr"/>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -2026,7 +2026,7 @@
       <c r="G31" s="5" t="inlineStr"/>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I31" s="4" t="inlineStr">
@@ -2175,7 +2175,7 @@
       <c r="G34" s="3" t="inlineStr"/>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2324,7 +2324,7 @@
       <c r="G37" s="5" t="inlineStr"/>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I37" s="4" t="inlineStr">
@@ -2473,7 +2473,7 @@
       <c r="G40" s="3" t="inlineStr"/>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
@@ -2622,7 +2622,7 @@
       <c r="G43" s="5" t="inlineStr"/>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I43" s="4" t="inlineStr">
@@ -2720,7 +2720,7 @@
       <c r="G45" s="3" t="inlineStr"/>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
@@ -2822,7 +2822,7 @@
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I47" s="4" t="inlineStr">
@@ -2869,7 +2869,7 @@
       <c r="G48" s="5" t="inlineStr"/>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I48" s="4" t="inlineStr">
@@ -2967,7 +2967,7 @@
       <c r="G50" s="3" t="inlineStr"/>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
@@ -3116,7 +3116,7 @@
       <c r="G53" s="3" t="inlineStr"/>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
@@ -3265,7 +3265,7 @@
       <c r="G56" s="3" t="inlineStr"/>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
@@ -3363,7 +3363,7 @@
       <c r="G58" s="5" t="inlineStr"/>
       <c r="H58" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I58" s="4" t="inlineStr">
@@ -3614,7 +3614,7 @@
       <c r="G63" s="3" t="inlineStr"/>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
@@ -3712,7 +3712,7 @@
       <c r="G65" s="5" t="inlineStr"/>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I65" s="4" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
@@ -3861,7 +3861,7 @@
       <c r="G68" s="3" t="inlineStr"/>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
@@ -4061,7 +4061,7 @@
       <c r="G72" s="5" t="inlineStr"/>
       <c r="H72" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I72" s="4" t="inlineStr">
@@ -4108,7 +4108,7 @@
       <c r="G73" s="3" t="inlineStr"/>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
@@ -4410,7 +4410,7 @@
       <c r="G79" s="5" t="inlineStr"/>
       <c r="H79" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I79" s="4" t="inlineStr">
@@ -4457,7 +4457,7 @@
       <c r="G80" s="3" t="inlineStr"/>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
@@ -4606,7 +4606,7 @@
       <c r="G83" s="3" t="inlineStr"/>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
@@ -4704,7 +4704,7 @@
       <c r="G85" s="5" t="inlineStr"/>
       <c r="H85" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I85" s="4" t="inlineStr">
@@ -4904,7 +4904,7 @@
       <c r="G89" s="3" t="inlineStr"/>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
@@ -5002,7 +5002,7 @@
       <c r="G91" s="5" t="inlineStr"/>
       <c r="H91" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I91" s="4" t="inlineStr">
@@ -5202,7 +5202,7 @@
       <c r="G95" s="3" t="inlineStr"/>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
@@ -5300,7 +5300,7 @@
       <c r="G97" s="5" t="inlineStr"/>
       <c r="H97" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I97" s="4" t="inlineStr">
@@ -5449,7 +5449,7 @@
       <c r="G100" s="3" t="inlineStr"/>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
@@ -5598,7 +5598,7 @@
       <c r="G103" s="3" t="inlineStr"/>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
@@ -5798,7 +5798,7 @@
       <c r="G107" s="5" t="inlineStr"/>
       <c r="H107" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I107" s="4" t="inlineStr">
@@ -5845,7 +5845,7 @@
       <c r="G108" s="3" t="inlineStr"/>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
@@ -6096,7 +6096,7 @@
       <c r="G113" s="5" t="inlineStr"/>
       <c r="H113" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I113" s="4" t="inlineStr">
@@ -6143,7 +6143,7 @@
       <c r="G114" s="3" t="inlineStr"/>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr">
@@ -6292,7 +6292,7 @@
       <c r="G117" s="3" t="inlineStr"/>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I117" s="2" t="inlineStr">
@@ -6390,7 +6390,7 @@
       <c r="G119" s="5" t="inlineStr"/>
       <c r="H119" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I119" s="4" t="inlineStr">
@@ -6539,7 +6539,7 @@
       <c r="G122" s="3" t="inlineStr"/>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I122" s="2" t="inlineStr">
@@ -6688,7 +6688,7 @@
       <c r="G125" s="5" t="inlineStr"/>
       <c r="H125" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I125" s="4" t="inlineStr">
@@ -6888,7 +6888,7 @@
       <c r="G129" s="3" t="inlineStr"/>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I129" s="2" t="inlineStr">
@@ -6986,7 +6986,7 @@
       <c r="G131" s="5" t="inlineStr"/>
       <c r="H131" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I131" s="4" t="inlineStr">
@@ -7135,7 +7135,7 @@
       <c r="G134" s="3" t="inlineStr"/>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I134" s="2" t="inlineStr">
@@ -7237,7 +7237,7 @@
       </c>
       <c r="H136" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I136" s="4" t="inlineStr">
@@ -7284,7 +7284,7 @@
       <c r="G137" s="5" t="inlineStr"/>
       <c r="H137" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I137" s="4" t="inlineStr">
@@ -7433,7 +7433,7 @@
       <c r="G140" s="3" t="inlineStr"/>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I140" s="2" t="inlineStr">
@@ -7578,7 +7578,7 @@
       <c r="G143" s="5" t="inlineStr"/>
       <c r="H143" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I143" s="4" t="inlineStr">
@@ -7676,7 +7676,7 @@
       <c r="G145" s="3" t="inlineStr"/>
       <c r="H145" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I145" s="2" t="inlineStr">
@@ -7821,7 +7821,7 @@
       <c r="G148" s="5" t="inlineStr"/>
       <c r="H148" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I148" s="4" t="inlineStr">
@@ -7919,7 +7919,7 @@
       <c r="G150" s="3" t="inlineStr"/>
       <c r="H150" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I150" s="2" t="inlineStr">
@@ -8068,7 +8068,7 @@
       <c r="G153" s="3" t="inlineStr"/>
       <c r="H153" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I153" s="2" t="inlineStr">
@@ -8315,7 +8315,7 @@
       <c r="G158" s="5" t="inlineStr"/>
       <c r="H158" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I158" s="4" t="inlineStr">
@@ -8362,7 +8362,7 @@
       <c r="G159" s="3" t="inlineStr"/>
       <c r="H159" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I159" s="2" t="inlineStr">
@@ -8562,7 +8562,7 @@
       <c r="G163" s="3" t="inlineStr"/>
       <c r="H163" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I163" s="2" t="inlineStr">
@@ -8660,7 +8660,7 @@
       <c r="G165" s="5" t="inlineStr"/>
       <c r="H165" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I165" s="4" t="inlineStr">
@@ -8809,7 +8809,7 @@
       <c r="G168" s="3" t="inlineStr"/>
       <c r="H168" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I168" s="2" t="inlineStr">
@@ -9005,7 +9005,7 @@
       <c r="G172" s="5" t="inlineStr"/>
       <c r="H172" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I172" s="4" t="inlineStr">
@@ -9103,7 +9103,7 @@
       <c r="G174" s="3" t="inlineStr"/>
       <c r="H174" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I174" s="2" t="inlineStr">
@@ -9252,7 +9252,7 @@
       <c r="G177" s="3" t="inlineStr"/>
       <c r="H177" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I177" s="2" t="inlineStr">
@@ -9346,7 +9346,7 @@
       <c r="G179" s="5" t="inlineStr"/>
       <c r="H179" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I179" s="4" t="inlineStr">
@@ -9448,7 +9448,7 @@
       </c>
       <c r="H181" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I181" s="2" t="inlineStr">
@@ -9546,7 +9546,7 @@
       <c r="G183" s="3" t="inlineStr"/>
       <c r="H183" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I183" s="2" t="inlineStr">
@@ -9644,7 +9644,7 @@
       <c r="G185" s="5" t="inlineStr"/>
       <c r="H185" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I185" s="4" t="inlineStr">
@@ -9844,7 +9844,7 @@
       <c r="G189" s="3" t="inlineStr"/>
       <c r="H189" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I189" s="2" t="inlineStr">
@@ -9942,7 +9942,7 @@
       <c r="G191" s="5" t="inlineStr"/>
       <c r="H191" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I191" s="4" t="inlineStr">
@@ -10091,7 +10091,7 @@
       <c r="G194" s="3" t="inlineStr"/>
       <c r="H194" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I194" s="2" t="inlineStr">
@@ -10240,7 +10240,7 @@
       <c r="G197" s="5" t="inlineStr"/>
       <c r="H197" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I197" s="4" t="inlineStr">
@@ -10291,7 +10291,7 @@
       </c>
       <c r="H198" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I198" s="2" t="inlineStr">
@@ -10389,7 +10389,7 @@
       <c r="G200" s="3" t="inlineStr"/>
       <c r="H200" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I200" s="2" t="inlineStr">
@@ -10459,7 +10459,7 @@
   <autoFilter ref="A1:K201"/>
   <dataValidations count="1">
     <dataValidation sqref="H2:H201" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Borrador,Sin borrador,Revisar_Juan,Enviado,Validado,Grabado"</formula1>
+      <formula1>"Borrador,Sin borrador,Por_revisar,Enviado,Validado,Grabado"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
@@ -10563,7 +10563,7 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
@@ -26344,7 +26344,7 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>Español redactado o adaptado por Claude (Revisar_Juan)</t>
+          <t>Español redactado o adaptado por Claude (Por_revisar)</t>
         </is>
       </c>
       <c r="B12" s="9" t="n">
